--- a/Modeling/Blender/shortcuts.xlsx
+++ b/Modeling/Blender/shortcuts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>快捷键</t>
   </si>
@@ -25,7 +25,7 @@
     <t>滚轮滚动</t>
   </si>
   <si>
-    <t>放缩视图</t>
+    <t>放缩视图 / 进度条放缩</t>
   </si>
   <si>
     <t>滚轮平移</t>
@@ -46,6 +46,18 @@
     <t>进入/退出 隔离模式</t>
   </si>
   <si>
+    <t>Tab</t>
+  </si>
+  <si>
+    <t>切换物体模式和编辑模式</t>
+  </si>
+  <si>
+    <t>Alt</t>
+  </si>
+  <si>
+    <t>循环选择</t>
+  </si>
+  <si>
     <t>Space (改键位)</t>
   </si>
   <si>
@@ -61,7 +73,7 @@
     <t>Shift + 滚轮</t>
   </si>
   <si>
-    <t>平移视图</t>
+    <t>平移视图 / 平移进度条</t>
   </si>
   <si>
     <t>Shift + A</t>
@@ -76,6 +88,18 @@
     <t>游标回到世界中心</t>
   </si>
   <si>
+    <t>Shift + S</t>
+  </si>
+  <si>
+    <t>选择吸附</t>
+  </si>
+  <si>
+    <t>Shift + Z</t>
+  </si>
+  <si>
+    <t>线框模式</t>
+  </si>
+  <si>
     <t>Ctrl + A</t>
   </si>
   <si>
@@ -91,7 +115,19 @@
     <t>Ctrl + L</t>
   </si>
   <si>
-    <t>材质关联(与最后选中的一致)</t>
+    <t>材质关联或复制修改器等(与最后选中的一致)</t>
+  </si>
+  <si>
+    <t>Ctrl + R</t>
+  </si>
+  <si>
+    <t>环切(滚动滚轮添加数量)</t>
+  </si>
+  <si>
+    <t>Ctrl + Alt + 0</t>
+  </si>
+  <si>
+    <t>设置摄像机视角为当前视角(需先创建摄像机)</t>
   </si>
   <si>
     <t>X / delete</t>
@@ -100,31 +136,34 @@
     <t>删除物体</t>
   </si>
   <si>
+    <t>Space + T</t>
+  </si>
+  <si>
+    <t>变换(transform)</t>
+  </si>
+  <si>
+    <t>Space + R</t>
+  </si>
+  <si>
+    <t>旋转(rotate) XYZ即沿该轴移动，后续可再跟角度制，按2下R为自由旋转</t>
+  </si>
+  <si>
+    <t>Space + G</t>
+  </si>
+  <si>
+    <t>平移 按Shift + XYZ即沿该垂直平面移动</t>
+  </si>
+  <si>
+    <t>Space + S</t>
+  </si>
+  <si>
+    <t>缩放(scale)</t>
+  </si>
+  <si>
     <t>T</t>
   </si>
   <si>
-    <t>变换(transform)</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>旋转(rotate)</t>
-  </si>
-  <si>
-    <t>XYZ即沿该轴移动，后续可再跟角度制，按2下R为自由旋转</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>平移</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>缩放(scale)</t>
+    <t>隐藏/显示 工具栏</t>
   </si>
   <si>
     <t>M</t>
@@ -133,10 +172,58 @@
     <t>将模型移动至集合(先选中物体)</t>
   </si>
   <si>
+    <t>合并点(编辑模式)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>打开侧边工具栏</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>插入关键帧(物体模式)</t>
+  </si>
+  <si>
+    <t>内插面(编辑模式)</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>挤出区域(编辑模式)</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>衰减编辑</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>开启快速收藏夹</t>
+  </si>
+  <si>
+    <t>Alt + D</t>
+  </si>
+  <si>
+    <t>关联复制</t>
+  </si>
+  <si>
     <t>Alt + R</t>
   </si>
   <si>
     <t>复位旋转</t>
+  </si>
+  <si>
+    <t>Alt + Z</t>
+  </si>
+  <si>
+    <t>透显模式</t>
   </si>
 </sst>
 </file>
@@ -144,10 +231,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -173,6 +260,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -180,11 +275,109 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -197,113 +390,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,67 +405,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,19 +567,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,91 +579,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,6 +596,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -527,30 +629,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -562,6 +640,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,7 +683,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,142 +699,142 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1145,11 +1232,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="30.875" customWidth="1"/>
+    <col min="2" max="2" width="64.125" customWidth="1"/>
     <col min="3" max="3" width="69.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1273,54 +1360,170 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
         <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A14:B16 A1:B4 A6:B12 A17 A18:B18" numberStoredAsText="1"/>
+    <ignoredError sqref="A15:B16 B24 A8:B9 A10 A11:B12 A1:B1 A2 A3:B4 A20:B20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Modeling/Blender/shortcuts.xlsx
+++ b/Modeling/Blender/shortcuts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>快捷键</t>
   </si>
@@ -112,6 +112,12 @@
     <t>物体表面细分</t>
   </si>
   <si>
+    <t>Ctrl + I</t>
+  </si>
+  <si>
+    <t>反选</t>
+  </si>
+  <si>
     <t>Ctrl + L</t>
   </si>
   <si>
@@ -196,6 +202,12 @@
     <t>挤出区域(编辑模式)</t>
   </si>
   <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>隐藏</t>
+  </si>
+  <si>
     <t>O</t>
   </si>
   <si>
@@ -212,6 +224,12 @@
   </si>
   <si>
     <t>关联复制</t>
+  </si>
+  <si>
+    <t>Alt + H</t>
+  </si>
+  <si>
+    <t>取消隐藏</t>
   </si>
   <si>
     <t>Alt + R</t>
@@ -1232,7 +1250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1408,22 +1426,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>42</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:2">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
       <c r="B23" t="s">
         <v>45</v>
       </c>
+      <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
@@ -1441,49 +1459,49 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>50</v>
       </c>
       <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>53</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
       <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
         <v>58</v>
       </c>
       <c r="C29" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>60</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1517,13 +1535,37 @@
       </c>
       <c r="B34" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A15:B16 B24 A8:B9 A10 A11:B12 A1:B1 A2 A3:B4 A20:B20" numberStoredAsText="1"/>
+    <ignoredError sqref="A15:B16 B25 A8:B9 A10 A11:B12 A1:B1 A2 A3:B4 A21:B21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>